--- a/test/fixtures/order-imports/serial-dates.xlsx
+++ b/test/fixtures/order-imports/serial-dates.xlsx
@@ -32,12 +32,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="60" formatCode="00000000000"/>
     <numFmt numFmtId="61" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="62" formatCode="yyyy-mm-dd hh:mm"/>
-    <numFmt numFmtId="63" formatCode="hh:mm"/>
+    <numFmt numFmtId="62" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="63" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="64" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -70,10 +71,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="62" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="61" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="62" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="63" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="64" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
